--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0002T0006Z000C1N18_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.67567485353876</v>
+        <v>3.197297163700048</v>
       </c>
       <c r="D2" t="n">
-        <v>2.495507198447987</v>
+        <v>0.4055199197477979</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
